--- a/data_extactor/batch_10_fa/trimmed/batch_0018_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0018_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | ریاضیات | علوم | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | علوم | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | مکانیک | طراحی | ترابری | ریاضیات | فیزیک | ساختمان و سازه</t>
+          <t>مهندسی و فناوری | مکانیک | طراحی | حمل و نقل | ریاضیات | فیزیک | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی</t>
+          <t>استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | مهندسان عمران | مهندسان برق | مهندسان صنایع | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان کشتی و موتورخانه</t>
+          <t>مهندسان هوافضا | مهندسان عمران | مهندسان برق | مهندسان صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان فنی کشتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>علوم | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>علوم | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | تکنسین‌های شیمی | شیمیدانان | مهندسان صنایع | مهندسان ساخت و تولید | دانشمندان علم مواد | مهندسان نانوسامانه‌ها</t>
+          <t>مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان صنایع | مهندسان تولید و ساخت | کارشناسان و دانشمندان علوم مواد | مهندسان نانوسیستم‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | ریاضیات | علوم | یادگیری فعال | نگارش | سخن گفتن | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | ریاضیات | علوم | یادگیری فعال | نگارش | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان خودرو | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مهندسان ساخت و تولید | کاردان‌ها و تکنسین‌های مهندسی مکانیک</t>
+          <t>مهندسان خودرو | مهندسان برق | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | علوم | نگارش | سخن گفتن | شنیدن فعال | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان خودرو | مهندسان شیمی | مهندسان برق | مهندسان انرژی (به‌جز بادی و خورشیدی) | دانشمندان علم مواد | مهندسان مکانیک | مهندسان سامانه‌های خورشیدی</t>
+          <t>مهندسان خودرو | مهندسان شیمی | مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | کارشناسان و دانشمندان علوم مواد | مهندسان مکانیک | مهندسان سیستم‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | شنیدن فعال | یادگیری فعال | علوم | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | گوش دادن فعال | یادگیری فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | فیزیک | ریاضیات | مکانیک | طراحی | رایانه و الکترونیک | ترابری</t>
+          <t>مهندسی و فناوری | فیزیک | ریاضیات | مکانیک | طراحی | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | مهندسان برق | مهندسان صنایع | مهندسان ساخت و تولید | مهندسان مکانیک | مهندسان مکاترونیک</t>
+          <t>تکنسین‌های مهندسی خودرو | مکانیک و تکنسین خدمات خودرو | مهندسان برق | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان مکانیک | مهندسان مکاترونیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | شنیدن فعال | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان عمران | اپراتورهای ماشین‌آلات حفاری مداوم معدن | کارشناسان مواد منفجره، مهمات و آتشباری | تکنسین‌های زمین‌شناسی (به‌جز هیدرولوژی) | دانشمندان علوم زمین (به‌جز هیدرولوژیست‌ها و جغرافیدانان) | مهندسان متالورژی و مواد | مهندسان نفت</t>
+          <t>مهندسان عمران | اپراتورهای ماشین‌های استخراج پیوسته | کارشناسان مواد منفجره و آتش‌باری | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | مهندسان متالورژی و مواد | مهندسان نفت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>علوم | تفکر انتقادی | نظارت | ریاضیات | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
+          <t>علوم | تفکر انتقادی | نظارت | ریاضیات | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی | درک کتبی</t>
+          <t>حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | درک کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | مهندسان انرژی (به‌جز بادی و خورشیدی) | مهندسان محیط زیست | مهندسان صنایع | تکنسین‌های پایش پرتوی هسته‌ای | اپراتورهای راکتور نیروگاه اتمی | تکنسین‌های هسته‌ای</t>
+          <t>مهندسان شیمی | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان محیط‌زیست | مهندسان صنایع | تکنسین‌های پایش و حفاظت پرتوی | اپراتورهای رآکتور نیروگاه هسته‌ای | تکنسین‌های هسته‌ای</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | مهندسان انرژی (به‌جز بادی و خورشیدی) | اپراتورهای پالایشگاه و تأسیسات گاز | تکنسین‌های زمین‌شناسی (به‌جز هیدرولوژی) | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | متصدیان سامانه‌های پمپاژ نفت، اپراتورهای پالایشگاه و اندازه‌گیران مخازن نفت | اپراتورهای تجهیزات خدمات چاه‌های نفت و گاز</t>
+          <t>مهندسان شیمی | مهندسان انرژی، به‌جز بادی و خورشیدی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای واحدهای خدمات چاه نفت و گاز</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان صنایع | مهندسان مکانیک | مهندسان محیط زیست</t>
+          <t>مهندسان هوافضا | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان صنایع | مهندسان مکانیک | مهندسان محیط‌زیست</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | علوم</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | ساختمان و سازه | مکانیک | طراحی | فیزیک | رایانه و الکترونیک</t>
+          <t>مهندسی و فناوری | ریاضیات | ساختمان و ساخت‌وساز | مکانیک | طراحی | فیزیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان برق | ممیزان انرژی | مهندسان محیط زیست | مکانیک‌ها و نصابان تأسیسات گرمایشی، تهویه مطبوع و برودتی | مهندسان مکانیک | اپراتورهای نیروگاه برق | مهندسان سامانه‌های خورشیدی</t>
+          <t>مهندسان برق | ممیزان انرژی | مهندسان محیط‌زیست | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | مهندسان مکانیک | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
